--- a/call-delivery/intake/2026-07/FE.xlsx
+++ b/call-delivery/intake/2026-07/FE.xlsx
@@ -17,11 +17,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +55,24 @@
     </font>
     <font>
       <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5AAC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -122,7 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,7 +150,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +163,38 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I218"/>
+  <dimension ref="B2:N218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -539,12 +590,21 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>CALL DELIVERY  —  Outbound Dialing Schedule (Intake)</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>GROUP STRATEGY &amp; NOTES  (carried over from July 2026 master)</t>
         </is>
       </c>
     </row>
@@ -555,6 +615,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>General Strategy</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -576,6 +643,11 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>M-F (3) Full Passes 1-AM &amp; 1 Afternoon &amp; 1 Evening + Clean Up Pass by TSC</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
@@ -593,8 +665,27 @@
           <t>Submitted Date:</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="17" t="n">
         <v>46220</v>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     1st Hour pass to jump start reps (prefer 2/wk to start at 7:05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>Additional "WFO Only" pass daily in the afternoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Ensure back-up agents/groups for inbound coverage</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -638,13 +729,18 @@
           <t>Special Instructions</t>
         </is>
       </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>If planning a Blitz, and to preserve records, only the AM+ WFO pass</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D10" s="10" t="n">
@@ -669,13 +765,18 @@
         </is>
       </c>
       <c r="I10" s="12" t="n"/>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>Saturdays will typically be for Blitzing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D11" s="10" t="n">
@@ -700,13 +801,18 @@
         </is>
       </c>
       <c r="I11" s="12" t="n"/>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>Initiatives</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D12" s="10" t="n">
@@ -737,7 +843,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D13" s="10" t="n">
@@ -758,13 +864,18 @@
         </is>
       </c>
       <c r="I13" s="12" t="n"/>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D14" s="10" t="n">
@@ -785,13 +896,28 @@
         </is>
       </c>
       <c r="I14" s="12" t="n"/>
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>List #</t>
+        </is>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="inlineStr">
+        <is>
+          <t>List Specific Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D15" s="10" t="n">
@@ -812,13 +938,20 @@
         </is>
       </c>
       <c r="I15" s="12" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>OM_ADHOC</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D16" s="10" t="n">
@@ -839,13 +972,20 @@
         </is>
       </c>
       <c r="I16" s="12" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>OM_CENTRAL_ALL</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D17" s="10" t="n">
@@ -866,13 +1006,20 @@
       </c>
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="12" t="n"/>
+      <c r="K17" s="20" t="n"/>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>OM_0SLOWPAY</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D18" s="10" t="n">
@@ -893,13 +1040,20 @@
       </c>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="12" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>OM_1PAY</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D19" s="10" t="n">
@@ -920,13 +1074,20 @@
         </is>
       </c>
       <c r="I19" s="12" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>OM_2PAY</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D20" s="10" t="n">
@@ -953,7 +1114,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D21" s="10" t="n">
@@ -974,13 +1135,18 @@
         </is>
       </c>
       <c r="I21" s="12" t="n"/>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Blitz Calendar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D22" s="10" t="n">
@@ -1001,13 +1167,33 @@
         </is>
       </c>
       <c r="I22" s="12" t="n"/>
+      <c r="K22" s="19" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="L22" s="19" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="M22" s="19" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
+        <is>
+          <t>FE PM</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D23" s="10" t="n">
@@ -1032,13 +1218,27 @@
         </is>
       </c>
       <c r="I23" s="12" t="n"/>
+      <c r="K23" s="22" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="n"/>
+      <c r="N23" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D24" s="10" t="n">
@@ -1063,13 +1263,27 @@
         </is>
       </c>
       <c r="I24" s="12" t="n"/>
+      <c r="K24" s="22" t="n">
+        <v>46205</v>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="n"/>
+      <c r="N24" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D25" s="10" t="n">
@@ -1090,13 +1304,23 @@
         </is>
       </c>
       <c r="I25" s="12" t="n"/>
+      <c r="K25" s="22" t="n">
+        <v>46206</v>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="n"/>
+      <c r="N25" s="20" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D26" s="10" t="n">
@@ -1117,13 +1341,23 @@
         </is>
       </c>
       <c r="I26" s="12" t="n"/>
+      <c r="K26" s="22" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="n"/>
+      <c r="N26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D27" s="10" t="n">
@@ -1144,13 +1378,23 @@
         </is>
       </c>
       <c r="I27" s="12" t="n"/>
+      <c r="K27" s="22" t="n">
+        <v>46208</v>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="M27" s="20" t="n"/>
+      <c r="N27" s="20" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D28" s="10" t="n">
@@ -1171,13 +1415,27 @@
         </is>
       </c>
       <c r="I28" s="12" t="n"/>
+      <c r="K28" s="22" t="n">
+        <v>46209</v>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="M28" s="20" t="n"/>
+      <c r="N28" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D29" s="10" t="n">
@@ -1198,13 +1456,27 @@
       </c>
       <c r="H29" s="11" t="n"/>
       <c r="I29" s="12" t="n"/>
+      <c r="K29" s="22" t="n">
+        <v>46210</v>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="n"/>
+      <c r="N29" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D30" s="10" t="n">
@@ -1225,13 +1497,27 @@
       </c>
       <c r="H30" s="11" t="n"/>
       <c r="I30" s="12" t="n"/>
+      <c r="K30" s="22" t="n">
+        <v>46211</v>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="M30" s="20" t="n"/>
+      <c r="N30" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D31" s="10" t="n">
@@ -1252,13 +1538,23 @@
       </c>
       <c r="H31" s="11" t="n"/>
       <c r="I31" s="12" t="n"/>
+      <c r="K31" s="22" t="n">
+        <v>46212</v>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="M31" s="20" t="n"/>
+      <c r="N31" s="20" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D32" s="10" t="n">
@@ -1279,13 +1575,27 @@
         </is>
       </c>
       <c r="I32" s="12" t="n"/>
+      <c r="K32" s="22" t="n">
+        <v>46213</v>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="M32" s="20" t="n"/>
+      <c r="N32" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D33" s="10" t="n">
@@ -1306,13 +1616,27 @@
         </is>
       </c>
       <c r="I33" s="12" t="n"/>
+      <c r="K33" s="22" t="n">
+        <v>46214</v>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="M33" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N33" s="20" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D34" s="10" t="n">
@@ -1333,13 +1657,27 @@
         </is>
       </c>
       <c r="I34" s="12" t="n"/>
+      <c r="K34" s="22" t="n">
+        <v>46215</v>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="M34" s="20" t="n"/>
+      <c r="N34" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D35" s="10" t="n">
@@ -1360,13 +1698,27 @@
         </is>
       </c>
       <c r="I35" s="12" t="n"/>
+      <c r="K35" s="22" t="n">
+        <v>46216</v>
+      </c>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="M35" s="20" t="n"/>
+      <c r="N35" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D36" s="10" t="n">
@@ -1391,13 +1743,23 @@
         </is>
       </c>
       <c r="I36" s="12" t="n"/>
+      <c r="K36" s="22" t="n">
+        <v>46217</v>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="M36" s="20" t="n"/>
+      <c r="N36" s="20" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D37" s="10" t="n">
@@ -1422,13 +1784,27 @@
         </is>
       </c>
       <c r="I37" s="12" t="n"/>
+      <c r="K37" s="22" t="n">
+        <v>46218</v>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="M37" s="20" t="n"/>
+      <c r="N37" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D38" s="10" t="n">
@@ -1449,13 +1825,23 @@
         </is>
       </c>
       <c r="I38" s="12" t="n"/>
+      <c r="K38" s="22" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="M38" s="20" t="n"/>
+      <c r="N38" s="20" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D39" s="10" t="n">
@@ -1476,13 +1862,27 @@
         </is>
       </c>
       <c r="I39" s="12" t="n"/>
+      <c r="K39" s="22" t="n">
+        <v>46220</v>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="M39" s="20" t="n"/>
+      <c r="N39" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D40" s="10" t="n">
@@ -1503,13 +1903,31 @@
         </is>
       </c>
       <c r="I40" s="12" t="n"/>
+      <c r="K40" s="22" t="n">
+        <v>46221</v>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N40" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D41" s="10" t="n">
@@ -1530,13 +1948,27 @@
         </is>
       </c>
       <c r="I41" s="12" t="n"/>
+      <c r="K41" s="22" t="n">
+        <v>46222</v>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="M41" s="20" t="n"/>
+      <c r="N41" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D42" s="10" t="n">
@@ -1557,13 +1989,27 @@
       </c>
       <c r="H42" s="11" t="n"/>
       <c r="I42" s="12" t="n"/>
+      <c r="K42" s="22" t="n">
+        <v>46223</v>
+      </c>
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="M42" s="20" t="n"/>
+      <c r="N42" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D43" s="10" t="n">
@@ -1584,13 +2030,23 @@
       </c>
       <c r="H43" s="11" t="n"/>
       <c r="I43" s="12" t="n"/>
+      <c r="K43" s="22" t="n">
+        <v>46224</v>
+      </c>
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="M43" s="20" t="n"/>
+      <c r="N43" s="20" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D44" s="10" t="n">
@@ -1611,13 +2067,27 @@
       </c>
       <c r="H44" s="11" t="n"/>
       <c r="I44" s="12" t="n"/>
+      <c r="K44" s="22" t="n">
+        <v>46225</v>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="M44" s="20" t="n"/>
+      <c r="N44" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D45" s="10" t="n">
@@ -1638,13 +2108,23 @@
         </is>
       </c>
       <c r="I45" s="12" t="n"/>
+      <c r="K45" s="22" t="n">
+        <v>46226</v>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="M45" s="20" t="n"/>
+      <c r="N45" s="20" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D46" s="10" t="n">
@@ -1665,13 +2145,27 @@
         </is>
       </c>
       <c r="I46" s="12" t="n"/>
+      <c r="K46" s="22" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="M46" s="20" t="n"/>
+      <c r="N46" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D47" s="10" t="n">
@@ -1692,13 +2186,31 @@
       </c>
       <c r="H47" s="11" t="n"/>
       <c r="I47" s="12" t="n"/>
+      <c r="K47" s="22" t="n">
+        <v>46228</v>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="M47" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N47" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D48" s="10" t="n">
@@ -1719,13 +2231,27 @@
       </c>
       <c r="H48" s="11" t="n"/>
       <c r="I48" s="12" t="n"/>
+      <c r="K48" s="22" t="n">
+        <v>46229</v>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="M48" s="20" t="n"/>
+      <c r="N48" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D49" s="10" t="n">
@@ -1746,13 +2272,27 @@
         </is>
       </c>
       <c r="I49" s="12" t="n"/>
+      <c r="K49" s="22" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="M49" s="20" t="n"/>
+      <c r="N49" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D50" s="10" t="n">
@@ -1777,13 +2317,27 @@
         </is>
       </c>
       <c r="I50" s="12" t="n"/>
+      <c r="K50" s="22" t="n">
+        <v>46231</v>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="M50" s="20" t="n"/>
+      <c r="N50" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D51" s="10" t="n">
@@ -1808,13 +2362,27 @@
         </is>
       </c>
       <c r="I51" s="12" t="n"/>
+      <c r="K51" s="22" t="n">
+        <v>46232</v>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="M51" s="20" t="n"/>
+      <c r="N51" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="C52" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D52" s="10" t="n">
@@ -1835,13 +2403,27 @@
         </is>
       </c>
       <c r="I52" s="12" t="n"/>
+      <c r="K52" s="22" t="n">
+        <v>46233</v>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="M52" s="20" t="n"/>
+      <c r="N52" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="B53" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D53" s="10" t="n">
@@ -1862,13 +2444,27 @@
         </is>
       </c>
       <c r="I53" s="12" t="n"/>
+      <c r="K53" s="22" t="n">
+        <v>46234</v>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="M53" s="20" t="n"/>
+      <c r="N53" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C54" s="9" t="n">
+      <c r="C54" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D54" s="10" t="n">
@@ -1889,13 +2485,21 @@
         </is>
       </c>
       <c r="I54" s="12" t="n"/>
+      <c r="L54" s="24" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="M54" s="25" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D55" s="10" t="n">
@@ -1922,7 +2526,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="18" t="n">
         <v>46214</v>
       </c>
       <c r="D56" s="10" t="n">
@@ -1949,7 +2553,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="18" t="n">
         <v>46215</v>
       </c>
       <c r="D57" s="10" t="n">
@@ -1976,7 +2580,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D58" s="10" t="n">
@@ -2007,7 +2611,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C59" s="9" t="n">
+      <c r="C59" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D59" s="10" t="n">
@@ -2038,7 +2642,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C60" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D60" s="10" t="n">
@@ -2069,7 +2673,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C61" s="9" t="n">
+      <c r="C61" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D61" s="10" t="n">
@@ -2096,7 +2700,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C62" s="9" t="n">
+      <c r="C62" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D62" s="10" t="n">
@@ -2123,7 +2727,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C63" s="9" t="n">
+      <c r="C63" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D63" s="10" t="n">
@@ -2150,7 +2754,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C64" s="9" t="n">
+      <c r="C64" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D64" s="10" t="n">
@@ -2177,7 +2781,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C65" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D65" s="10" t="n">
@@ -2204,7 +2808,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C66" s="9" t="n">
+      <c r="C66" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D66" s="10" t="n">
@@ -2231,7 +2835,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C67" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D67" s="10" t="n">
@@ -2258,7 +2862,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C68" s="9" t="n">
+      <c r="C68" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D68" s="10" t="n">
@@ -2285,7 +2889,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C69" s="9" t="n">
+      <c r="C69" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D69" s="10" t="n">
@@ -2312,7 +2916,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C70" s="9" t="n">
+      <c r="C70" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D70" s="10" t="n">
@@ -2339,7 +2943,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C71" s="9" t="n">
+      <c r="C71" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D71" s="10" t="n">
@@ -2366,7 +2970,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C72" s="9" t="n">
+      <c r="C72" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D72" s="10" t="n">
@@ -2397,7 +3001,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C73" s="9" t="n">
+      <c r="C73" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D73" s="10" t="n">
@@ -2428,7 +3032,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="C74" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D74" s="10" t="n">
@@ -2455,7 +3059,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="C75" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D75" s="10" t="n">
@@ -2482,7 +3086,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C76" s="9" t="n">
+      <c r="C76" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D76" s="10" t="n">
@@ -2509,7 +3113,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C77" s="9" t="n">
+      <c r="C77" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D77" s="10" t="n">
@@ -2536,7 +3140,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C78" s="9" t="n">
+      <c r="C78" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D78" s="10" t="n">
@@ -2563,7 +3167,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C79" s="9" t="n">
+      <c r="C79" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D79" s="10" t="n">
@@ -2590,7 +3194,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C80" s="9" t="n">
+      <c r="C80" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D80" s="10" t="n">
@@ -2617,7 +3221,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C81" s="9" t="n">
+      <c r="C81" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D81" s="10" t="n">
@@ -2644,7 +3248,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C82" s="9" t="n">
+      <c r="C82" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D82" s="10" t="n">
@@ -2671,7 +3275,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C83" s="9" t="n">
+      <c r="C83" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D83" s="10" t="n">
@@ -2698,7 +3302,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C84" s="9" t="n">
+      <c r="C84" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D84" s="10" t="n">
@@ -2725,7 +3329,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C85" s="9" t="n">
+      <c r="C85" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D85" s="10" t="n">
@@ -2752,7 +3356,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="C86" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D86" s="10" t="n">
@@ -2783,7 +3387,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C87" s="9" t="n">
+      <c r="C87" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D87" s="10" t="n">
@@ -2814,7 +3418,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C88" s="9" t="n">
+      <c r="C88" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D88" s="10" t="n">
@@ -2841,7 +3445,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C89" s="9" t="n">
+      <c r="C89" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D89" s="10" t="n">
@@ -2868,7 +3472,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C90" s="9" t="n">
+      <c r="C90" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D90" s="10" t="n">
@@ -2895,7 +3499,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C91" s="9" t="n">
+      <c r="C91" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D91" s="10" t="n">
@@ -2922,7 +3526,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C92" s="9" t="n">
+      <c r="C92" s="18" t="n">
         <v>46221</v>
       </c>
       <c r="D92" s="10" t="n">
@@ -2949,7 +3553,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C93" s="9" t="n">
+      <c r="C93" s="18" t="n">
         <v>46221</v>
       </c>
       <c r="D93" s="10" t="n">
@@ -2976,7 +3580,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C94" s="9" t="n">
+      <c r="C94" s="18" t="n">
         <v>46222</v>
       </c>
       <c r="D94" s="10" t="n">
@@ -3003,7 +3607,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C95" s="9" t="n">
+      <c r="C95" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D95" s="10" t="n">
@@ -3034,7 +3638,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C96" s="9" t="n">
+      <c r="C96" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D96" s="10" t="n">
@@ -3065,7 +3669,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C97" s="9" t="n">
+      <c r="C97" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D97" s="10" t="n">
@@ -3096,7 +3700,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C98" s="9" t="n">
+      <c r="C98" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D98" s="10" t="n">
@@ -3123,7 +3727,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C99" s="9" t="n">
+      <c r="C99" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D99" s="10" t="n">
@@ -3150,7 +3754,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C100" s="9" t="n">
+      <c r="C100" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D100" s="10" t="n">
@@ -3177,7 +3781,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C101" s="9" t="n">
+      <c r="C101" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D101" s="10" t="n">
@@ -3204,7 +3808,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C102" s="9" t="n">
+      <c r="C102" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D102" s="10" t="n">
@@ -3231,7 +3835,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C103" s="9" t="n">
+      <c r="C103" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D103" s="10" t="n">
@@ -3258,7 +3862,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C104" s="9" t="n">
+      <c r="C104" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D104" s="10" t="n">
@@ -3285,7 +3889,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C105" s="9" t="n">
+      <c r="C105" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D105" s="10" t="n">
@@ -3312,7 +3916,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C106" s="9" t="n">
+      <c r="C106" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D106" s="10" t="n">
@@ -3339,7 +3943,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C107" s="9" t="n">
+      <c r="C107" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D107" s="10" t="n">
@@ -3366,7 +3970,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C108" s="9" t="n">
+      <c r="C108" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D108" s="10" t="n">
@@ -3393,7 +3997,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C109" s="9" t="n">
+      <c r="C109" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D109" s="10" t="n">
@@ -3424,7 +4028,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C110" s="9" t="n">
+      <c r="C110" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D110" s="10" t="n">
@@ -3455,7 +4059,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C111" s="9" t="n">
+      <c r="C111" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D111" s="10" t="n">
@@ -3482,7 +4086,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C112" s="9" t="n">
+      <c r="C112" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D112" s="10" t="n">
@@ -3509,7 +4113,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C113" s="9" t="n">
+      <c r="C113" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D113" s="10" t="n">
@@ -3536,7 +4140,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C114" s="9" t="n">
+      <c r="C114" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D114" s="10" t="n">
@@ -3563,7 +4167,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C115" s="9" t="n">
+      <c r="C115" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D115" s="10" t="n">
@@ -3590,7 +4194,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C116" s="9" t="n">
+      <c r="C116" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D116" s="10" t="n">
@@ -3617,7 +4221,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C117" s="9" t="n">
+      <c r="C117" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D117" s="10" t="n">
@@ -3644,7 +4248,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C118" s="9" t="n">
+      <c r="C118" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D118" s="10" t="n">
@@ -3671,7 +4275,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C119" s="9" t="n">
+      <c r="C119" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D119" s="10" t="n">
@@ -3698,7 +4302,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C120" s="9" t="n">
+      <c r="C120" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D120" s="10" t="n">
@@ -3725,7 +4329,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C121" s="9" t="n">
+      <c r="C121" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D121" s="10" t="n">
@@ -3752,7 +4356,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C122" s="9" t="n">
+      <c r="C122" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D122" s="10" t="n">
@@ -3783,7 +4387,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C123" s="9" t="n">
+      <c r="C123" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D123" s="10" t="n">
@@ -3814,7 +4418,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C124" s="9" t="n">
+      <c r="C124" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D124" s="10" t="n">
@@ -3841,7 +4445,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C125" s="9" t="n">
+      <c r="C125" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D125" s="10" t="n">
@@ -3868,7 +4472,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C126" s="9" t="n">
+      <c r="C126" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D126" s="10" t="n">
@@ -3895,7 +4499,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C127" s="9" t="n">
+      <c r="C127" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D127" s="10" t="n">
@@ -3922,7 +4526,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C128" s="9" t="n">
+      <c r="C128" s="18" t="n">
         <v>46228</v>
       </c>
       <c r="D128" s="10" t="n">
@@ -3949,7 +4553,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C129" s="9" t="n">
+      <c r="C129" s="18" t="n">
         <v>46228</v>
       </c>
       <c r="D129" s="10" t="n">
@@ -3976,7 +4580,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C130" s="9" t="n">
+      <c r="C130" s="18" t="n">
         <v>46229</v>
       </c>
       <c r="D130" s="10" t="n">
@@ -4003,7 +4607,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C131" s="9" t="n">
+      <c r="C131" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D131" s="10" t="n">
@@ -4034,7 +4638,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C132" s="9" t="n">
+      <c r="C132" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D132" s="10" t="n">
@@ -4065,7 +4669,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C133" s="9" t="n">
+      <c r="C133" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D133" s="10" t="n">
@@ -4096,7 +4700,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C134" s="9" t="n">
+      <c r="C134" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D134" s="10" t="n">
@@ -4123,7 +4727,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C135" s="9" t="n">
+      <c r="C135" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D135" s="10" t="n">
@@ -4150,7 +4754,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C136" s="9" t="n">
+      <c r="C136" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D136" s="10" t="n">
@@ -4177,7 +4781,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C137" s="9" t="n">
+      <c r="C137" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D137" s="10" t="n">
@@ -4204,7 +4808,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C138" s="9" t="n">
+      <c r="C138" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D138" s="10" t="n">
@@ -4231,7 +4835,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C139" s="9" t="n">
+      <c r="C139" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D139" s="10" t="n">
@@ -4258,7 +4862,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C140" s="9" t="n">
+      <c r="C140" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D140" s="10" t="n">
@@ -4285,7 +4889,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C141" s="9" t="n">
+      <c r="C141" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D141" s="10" t="n">
@@ -4312,7 +4916,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C142" s="9" t="n">
+      <c r="C142" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D142" s="10" t="n">
@@ -4339,7 +4943,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C143" s="9" t="n">
+      <c r="C143" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D143" s="10" t="n">
@@ -4366,7 +4970,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C144" s="9" t="n">
+      <c r="C144" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D144" s="10" t="n">
@@ -4397,7 +5001,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C145" s="9" t="n">
+      <c r="C145" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D145" s="10" t="n">
@@ -4428,7 +5032,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C146" s="9" t="n">
+      <c r="C146" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D146" s="10" t="n">
@@ -4455,7 +5059,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C147" s="9" t="n">
+      <c r="C147" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D147" s="10" t="n">
@@ -4482,7 +5086,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C148" s="9" t="n">
+      <c r="C148" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D148" s="10" t="n">
@@ -4509,7 +5113,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C149" s="9" t="n">
+      <c r="C149" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D149" s="10" t="n">
@@ -4536,7 +5140,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C150" s="9" t="n">
+      <c r="C150" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D150" s="10" t="n">
@@ -4563,7 +5167,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C151" s="9" t="n">
+      <c r="C151" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D151" s="10" t="n">
@@ -4590,7 +5194,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C152" s="9" t="n">
+      <c r="C152" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D152" s="10" t="n">
@@ -4617,7 +5221,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C153" s="9" t="n">
+      <c r="C153" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D153" s="10" t="n">
@@ -4644,7 +5248,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C154" s="9" t="n">
+      <c r="C154" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D154" s="10" t="n">
@@ -4671,7 +5275,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C155" s="9" t="n">
+      <c r="C155" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D155" s="10" t="n">
@@ -4698,7 +5302,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C156" s="9" t="n">
+      <c r="C156" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D156" s="10" t="n">
@@ -4725,7 +5329,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C157" s="9" t="n">
+      <c r="C157" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D157" s="10" t="n">
@@ -4756,7 +5360,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C158" s="9" t="n">
+      <c r="C158" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D158" s="10" t="n">
@@ -4787,7 +5391,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C159" s="9" t="n">
+      <c r="C159" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D159" s="10" t="n">
@@ -4814,7 +5418,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C160" s="9" t="n">
+      <c r="C160" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D160" s="10" t="n">
@@ -4841,7 +5445,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C161" s="9" t="n">
+      <c r="C161" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D161" s="10" t="n">
@@ -4868,7 +5472,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C162" s="9" t="n">
+      <c r="C162" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D162" s="10" t="n">
@@ -4895,7 +5499,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C163" s="9" t="n">
+      <c r="C163" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D163" s="10" t="n">
@@ -4926,7 +5530,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C164" s="9" t="n">
+      <c r="C164" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D164" s="10" t="n">
@@ -4957,7 +5561,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C165" s="9" t="n">
+      <c r="C165" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D165" s="10" t="n">
@@ -4984,7 +5588,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C166" s="9" t="n">
+      <c r="C166" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D166" s="10" t="n">
@@ -5011,7 +5615,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C167" s="9" t="n">
+      <c r="C167" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D167" s="10" t="n">
@@ -5038,7 +5642,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C168" s="9" t="n">
+      <c r="C168" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D168" s="10" t="n">
@@ -5065,7 +5669,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C169" s="9" t="n"/>
+      <c r="C169" s="18" t="n"/>
       <c r="D169" s="10" t="n"/>
       <c r="E169" s="11" t="n"/>
       <c r="F169" s="11" t="n"/>
@@ -5078,7 +5682,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C170" s="9" t="n"/>
+      <c r="C170" s="18" t="n"/>
       <c r="D170" s="10" t="n"/>
       <c r="E170" s="11" t="n"/>
       <c r="F170" s="11" t="n"/>
@@ -5091,7 +5695,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C171" s="9" t="n"/>
+      <c r="C171" s="18" t="n"/>
       <c r="D171" s="10" t="n"/>
       <c r="E171" s="11" t="n"/>
       <c r="F171" s="11" t="n"/>
@@ -5104,7 +5708,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C172" s="9" t="n"/>
+      <c r="C172" s="18" t="n"/>
       <c r="D172" s="10" t="n"/>
       <c r="E172" s="11" t="n"/>
       <c r="F172" s="11" t="n"/>
@@ -5117,7 +5721,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C173" s="9" t="n"/>
+      <c r="C173" s="18" t="n"/>
       <c r="D173" s="10" t="n"/>
       <c r="E173" s="11" t="n"/>
       <c r="F173" s="11" t="n"/>
@@ -5130,7 +5734,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C174" s="9" t="n"/>
+      <c r="C174" s="18" t="n"/>
       <c r="D174" s="10" t="n"/>
       <c r="E174" s="11" t="n"/>
       <c r="F174" s="11" t="n"/>
@@ -5143,7 +5747,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C175" s="9" t="n"/>
+      <c r="C175" s="18" t="n"/>
       <c r="D175" s="10" t="n"/>
       <c r="E175" s="11" t="n"/>
       <c r="F175" s="11" t="n"/>
@@ -5156,7 +5760,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C176" s="9" t="n"/>
+      <c r="C176" s="18" t="n"/>
       <c r="D176" s="10" t="n"/>
       <c r="E176" s="11" t="n"/>
       <c r="F176" s="11" t="n"/>
@@ -5169,7 +5773,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C177" s="9" t="n"/>
+      <c r="C177" s="18" t="n"/>
       <c r="D177" s="10" t="n"/>
       <c r="E177" s="11" t="n"/>
       <c r="F177" s="11" t="n"/>
@@ -5182,7 +5786,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C178" s="9" t="n"/>
+      <c r="C178" s="18" t="n"/>
       <c r="D178" s="10" t="n"/>
       <c r="E178" s="11" t="n"/>
       <c r="F178" s="11" t="n"/>
@@ -5195,7 +5799,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C179" s="9" t="n"/>
+      <c r="C179" s="18" t="n"/>
       <c r="D179" s="10" t="n"/>
       <c r="E179" s="11" t="n"/>
       <c r="F179" s="11" t="n"/>
@@ -5208,7 +5812,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C180" s="9" t="n"/>
+      <c r="C180" s="18" t="n"/>
       <c r="D180" s="10" t="n"/>
       <c r="E180" s="11" t="n"/>
       <c r="F180" s="11" t="n"/>
@@ -5221,7 +5825,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C181" s="9" t="n"/>
+      <c r="C181" s="18" t="n"/>
       <c r="D181" s="10" t="n"/>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
@@ -5234,7 +5838,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C182" s="9" t="n"/>
+      <c r="C182" s="18" t="n"/>
       <c r="D182" s="10" t="n"/>
       <c r="E182" s="11" t="n"/>
       <c r="F182" s="11" t="n"/>
@@ -5247,7 +5851,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C183" s="9" t="n"/>
+      <c r="C183" s="18" t="n"/>
       <c r="D183" s="10" t="n"/>
       <c r="E183" s="11" t="n"/>
       <c r="F183" s="11" t="n"/>
@@ -5260,7 +5864,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C184" s="9" t="n"/>
+      <c r="C184" s="18" t="n"/>
       <c r="D184" s="10" t="n"/>
       <c r="E184" s="11" t="n"/>
       <c r="F184" s="11" t="n"/>
@@ -5273,7 +5877,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C185" s="9" t="n"/>
+      <c r="C185" s="18" t="n"/>
       <c r="D185" s="10" t="n"/>
       <c r="E185" s="11" t="n"/>
       <c r="F185" s="11" t="n"/>
@@ -5286,7 +5890,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C186" s="9" t="n"/>
+      <c r="C186" s="18" t="n"/>
       <c r="D186" s="10" t="n"/>
       <c r="E186" s="11" t="n"/>
       <c r="F186" s="11" t="n"/>
@@ -5299,7 +5903,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C187" s="9" t="n"/>
+      <c r="C187" s="18" t="n"/>
       <c r="D187" s="10" t="n"/>
       <c r="E187" s="11" t="n"/>
       <c r="F187" s="11" t="n"/>
@@ -5312,7 +5916,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C188" s="9" t="n"/>
+      <c r="C188" s="18" t="n"/>
       <c r="D188" s="10" t="n"/>
       <c r="E188" s="11" t="n"/>
       <c r="F188" s="11" t="n"/>
@@ -5325,7 +5929,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C189" s="9" t="n"/>
+      <c r="C189" s="18" t="n"/>
       <c r="D189" s="10" t="n"/>
       <c r="E189" s="11" t="n"/>
       <c r="F189" s="11" t="n"/>
@@ -5338,7 +5942,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C190" s="9" t="n"/>
+      <c r="C190" s="18" t="n"/>
       <c r="D190" s="10" t="n"/>
       <c r="E190" s="11" t="n"/>
       <c r="F190" s="11" t="n"/>
@@ -5351,7 +5955,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C191" s="9" t="n"/>
+      <c r="C191" s="18" t="n"/>
       <c r="D191" s="10" t="n"/>
       <c r="E191" s="11" t="n"/>
       <c r="F191" s="11" t="n"/>
@@ -5364,7 +5968,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C192" s="9" t="n"/>
+      <c r="C192" s="18" t="n"/>
       <c r="D192" s="10" t="n"/>
       <c r="E192" s="11" t="n"/>
       <c r="F192" s="11" t="n"/>
@@ -5377,7 +5981,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C193" s="9" t="n"/>
+      <c r="C193" s="18" t="n"/>
       <c r="D193" s="10" t="n"/>
       <c r="E193" s="11" t="n"/>
       <c r="F193" s="11" t="n"/>
@@ -5390,7 +5994,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C194" s="9" t="n"/>
+      <c r="C194" s="18" t="n"/>
       <c r="D194" s="10" t="n"/>
       <c r="E194" s="11" t="n"/>
       <c r="F194" s="11" t="n"/>
@@ -5403,7 +6007,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C195" s="9" t="n"/>
+      <c r="C195" s="18" t="n"/>
       <c r="D195" s="10" t="n"/>
       <c r="E195" s="11" t="n"/>
       <c r="F195" s="11" t="n"/>
@@ -5416,7 +6020,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C196" s="9" t="n"/>
+      <c r="C196" s="18" t="n"/>
       <c r="D196" s="10" t="n"/>
       <c r="E196" s="11" t="n"/>
       <c r="F196" s="11" t="n"/>
@@ -5429,7 +6033,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C197" s="9" t="n"/>
+      <c r="C197" s="18" t="n"/>
       <c r="D197" s="10" t="n"/>
       <c r="E197" s="11" t="n"/>
       <c r="F197" s="11" t="n"/>
@@ -5442,7 +6046,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C198" s="9" t="n"/>
+      <c r="C198" s="18" t="n"/>
       <c r="D198" s="10" t="n"/>
       <c r="E198" s="11" t="n"/>
       <c r="F198" s="11" t="n"/>
@@ -5455,7 +6059,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C199" s="9" t="n"/>
+      <c r="C199" s="18" t="n"/>
       <c r="D199" s="10" t="n"/>
       <c r="E199" s="11" t="n"/>
       <c r="F199" s="11" t="n"/>
@@ -5468,7 +6072,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C200" s="9" t="n"/>
+      <c r="C200" s="18" t="n"/>
       <c r="D200" s="10" t="n"/>
       <c r="E200" s="11" t="n"/>
       <c r="F200" s="11" t="n"/>
@@ -5481,7 +6085,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C201" s="9" t="n"/>
+      <c r="C201" s="18" t="n"/>
       <c r="D201" s="10" t="n"/>
       <c r="E201" s="11" t="n"/>
       <c r="F201" s="11" t="n"/>
@@ -5494,7 +6098,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C202" s="9" t="n"/>
+      <c r="C202" s="18" t="n"/>
       <c r="D202" s="10" t="n"/>
       <c r="E202" s="11" t="n"/>
       <c r="F202" s="11" t="n"/>
@@ -5507,7 +6111,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C203" s="9" t="n"/>
+      <c r="C203" s="18" t="n"/>
       <c r="D203" s="10" t="n"/>
       <c r="E203" s="11" t="n"/>
       <c r="F203" s="11" t="n"/>
@@ -5520,7 +6124,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C204" s="9" t="n"/>
+      <c r="C204" s="18" t="n"/>
       <c r="D204" s="10" t="n"/>
       <c r="E204" s="11" t="n"/>
       <c r="F204" s="11" t="n"/>
@@ -5533,7 +6137,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C205" s="9" t="n"/>
+      <c r="C205" s="18" t="n"/>
       <c r="D205" s="10" t="n"/>
       <c r="E205" s="11" t="n"/>
       <c r="F205" s="11" t="n"/>
@@ -5546,7 +6150,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C206" s="9" t="n"/>
+      <c r="C206" s="18" t="n"/>
       <c r="D206" s="10" t="n"/>
       <c r="E206" s="11" t="n"/>
       <c r="F206" s="11" t="n"/>
@@ -5559,7 +6163,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C207" s="9" t="n"/>
+      <c r="C207" s="18" t="n"/>
       <c r="D207" s="10" t="n"/>
       <c r="E207" s="11" t="n"/>
       <c r="F207" s="11" t="n"/>
@@ -5572,7 +6176,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C208" s="9" t="n"/>
+      <c r="C208" s="18" t="n"/>
       <c r="D208" s="10" t="n"/>
       <c r="E208" s="11" t="n"/>
       <c r="F208" s="11" t="n"/>
@@ -5585,7 +6189,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C209" s="9" t="n"/>
+      <c r="C209" s="18" t="n"/>
       <c r="D209" s="10" t="n"/>
       <c r="E209" s="11" t="n"/>
       <c r="F209" s="11" t="n"/>
@@ -5598,7 +6202,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C210" s="9" t="n"/>
+      <c r="C210" s="18" t="n"/>
       <c r="D210" s="10" t="n"/>
       <c r="E210" s="11" t="n"/>
       <c r="F210" s="11" t="n"/>
@@ -5611,7 +6215,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C211" s="9" t="n"/>
+      <c r="C211" s="18" t="n"/>
       <c r="D211" s="10" t="n"/>
       <c r="E211" s="11" t="n"/>
       <c r="F211" s="11" t="n"/>
@@ -5624,7 +6228,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C212" s="9" t="n"/>
+      <c r="C212" s="18" t="n"/>
       <c r="D212" s="10" t="n"/>
       <c r="E212" s="11" t="n"/>
       <c r="F212" s="11" t="n"/>
@@ -5637,7 +6241,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C213" s="9" t="n"/>
+      <c r="C213" s="18" t="n"/>
       <c r="D213" s="10" t="n"/>
       <c r="E213" s="11" t="n"/>
       <c r="F213" s="11" t="n"/>
@@ -5650,7 +6254,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C214" s="9" t="n"/>
+      <c r="C214" s="18" t="n"/>
       <c r="D214" s="10" t="n"/>
       <c r="E214" s="11" t="n"/>
       <c r="F214" s="11" t="n"/>
@@ -5663,7 +6267,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C215" s="9" t="n"/>
+      <c r="C215" s="18" t="n"/>
       <c r="D215" s="10" t="n"/>
       <c r="E215" s="11" t="n"/>
       <c r="F215" s="11" t="n"/>
@@ -5676,7 +6280,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C216" s="9" t="n"/>
+      <c r="C216" s="18" t="n"/>
       <c r="D216" s="10" t="n"/>
       <c r="E216" s="11" t="n"/>
       <c r="F216" s="11" t="n"/>
@@ -5689,7 +6293,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C217" s="9" t="n"/>
+      <c r="C217" s="18" t="n"/>
       <c r="D217" s="10" t="n"/>
       <c r="E217" s="11" t="n"/>
       <c r="F217" s="11" t="n"/>
@@ -5702,7 +6306,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C218" s="9" t="n"/>
+      <c r="C218" s="18" t="n"/>
       <c r="D218" s="10" t="n"/>
       <c r="E218" s="11" t="n"/>
       <c r="F218" s="11" t="n"/>
@@ -5711,9 +6315,18 @@
       <c r="I218" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="11">
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K11:N11"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K5:N5"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/call-delivery/intake/2026-07/FE.xlsx
+++ b/call-delivery/intake/2026-07/FE.xlsx
@@ -272,8 +272,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblSchedule" displayName="tblSchedule" ref="B9:I218" headerRowCount="1">
-  <autoFilter ref="B9:I218"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblSchedule" displayName="tblSchedule" ref="B9:I212" headerRowCount="1">
+  <autoFilter ref="B9:I212"/>
   <tableColumns count="8">
     <tableColumn id="2" name="Business Group"/>
     <tableColumn id="3" name="Date"/>
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N218"/>
+  <dimension ref="B2:N212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5499,30 +5499,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C163" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D163" s="10" t="n">
-        <v>0.3541666666666667</v>
-      </c>
-      <c r="E163" s="11" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="F163" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G163" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H163" s="11" t="inlineStr">
-        <is>
-          <t>AMs</t>
-        </is>
-      </c>
+      <c r="C163" s="18" t="n"/>
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="11" t="n"/>
+      <c r="F163" s="11" t="n"/>
+      <c r="G163" s="11" t="n"/>
+      <c r="H163" s="11" t="n"/>
       <c r="I163" s="12" t="n"/>
     </row>
     <row r="164">
@@ -5530,30 +5512,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C164" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D164" s="10" t="n">
-        <v>0.4583333333333333</v>
-      </c>
-      <c r="E164" s="11" t="inlineStr">
-        <is>
-          <t>C-M-P</t>
-        </is>
-      </c>
-      <c r="F164" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G164" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H164" s="11" t="inlineStr">
-        <is>
-          <t>AMs</t>
-        </is>
-      </c>
+      <c r="C164" s="18" t="n"/>
+      <c r="D164" s="10" t="n"/>
+      <c r="E164" s="11" t="n"/>
+      <c r="F164" s="11" t="n"/>
+      <c r="G164" s="11" t="n"/>
+      <c r="H164" s="11" t="n"/>
       <c r="I164" s="12" t="n"/>
     </row>
     <row r="165">
@@ -5561,26 +5525,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C165" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D165" s="10" t="n">
-        <v>0.5208333333333334</v>
-      </c>
+      <c r="C165" s="18" t="n"/>
+      <c r="D165" s="10" t="n"/>
       <c r="E165" s="11" t="n"/>
-      <c r="F165" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G165" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H165" s="11" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
+      <c r="F165" s="11" t="n"/>
+      <c r="G165" s="11" t="n"/>
+      <c r="H165" s="11" t="n"/>
       <c r="I165" s="12" t="n"/>
     </row>
     <row r="166">
@@ -5588,26 +5538,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C166" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D166" s="10" t="n">
-        <v>0.5625</v>
-      </c>
+      <c r="C166" s="18" t="n"/>
+      <c r="D166" s="10" t="n"/>
       <c r="E166" s="11" t="n"/>
-      <c r="F166" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G166" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H166" s="11" t="inlineStr">
-        <is>
-          <t>WFO</t>
-        </is>
-      </c>
+      <c r="F166" s="11" t="n"/>
+      <c r="G166" s="11" t="n"/>
+      <c r="H166" s="11" t="n"/>
       <c r="I166" s="12" t="n"/>
     </row>
     <row r="167">
@@ -5615,26 +5551,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C167" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D167" s="10" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="C167" s="18" t="n"/>
+      <c r="D167" s="10" t="n"/>
       <c r="E167" s="11" t="n"/>
-      <c r="F167" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G167" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H167" s="11" t="inlineStr">
-        <is>
-          <t>Blitz</t>
-        </is>
-      </c>
+      <c r="F167" s="11" t="n"/>
+      <c r="G167" s="11" t="n"/>
+      <c r="H167" s="11" t="n"/>
       <c r="I167" s="12" t="n"/>
     </row>
     <row r="168">
@@ -5642,26 +5564,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C168" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D168" s="10" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="C168" s="18" t="n"/>
+      <c r="D168" s="10" t="n"/>
       <c r="E168" s="11" t="n"/>
-      <c r="F168" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G168" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H168" s="11" t="inlineStr">
-        <is>
-          <t>TSC (All)</t>
-        </is>
-      </c>
+      <c r="F168" s="11" t="n"/>
+      <c r="G168" s="11" t="n"/>
+      <c r="H168" s="11" t="n"/>
       <c r="I168" s="12" t="n"/>
     </row>
     <row r="169">
@@ -6235,84 +6143,6 @@
       <c r="G212" s="11" t="n"/>
       <c r="H212" s="11" t="n"/>
       <c r="I212" s="12" t="n"/>
-    </row>
-    <row r="213">
-      <c r="B213" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C213" s="18" t="n"/>
-      <c r="D213" s="10" t="n"/>
-      <c r="E213" s="11" t="n"/>
-      <c r="F213" s="11" t="n"/>
-      <c r="G213" s="11" t="n"/>
-      <c r="H213" s="11" t="n"/>
-      <c r="I213" s="12" t="n"/>
-    </row>
-    <row r="214">
-      <c r="B214" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C214" s="18" t="n"/>
-      <c r="D214" s="10" t="n"/>
-      <c r="E214" s="11" t="n"/>
-      <c r="F214" s="11" t="n"/>
-      <c r="G214" s="11" t="n"/>
-      <c r="H214" s="11" t="n"/>
-      <c r="I214" s="12" t="n"/>
-    </row>
-    <row r="215">
-      <c r="B215" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C215" s="18" t="n"/>
-      <c r="D215" s="10" t="n"/>
-      <c r="E215" s="11" t="n"/>
-      <c r="F215" s="11" t="n"/>
-      <c r="G215" s="11" t="n"/>
-      <c r="H215" s="11" t="n"/>
-      <c r="I215" s="12" t="n"/>
-    </row>
-    <row r="216">
-      <c r="B216" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C216" s="18" t="n"/>
-      <c r="D216" s="10" t="n"/>
-      <c r="E216" s="11" t="n"/>
-      <c r="F216" s="11" t="n"/>
-      <c r="G216" s="11" t="n"/>
-      <c r="H216" s="11" t="n"/>
-      <c r="I216" s="12" t="n"/>
-    </row>
-    <row r="217">
-      <c r="B217" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C217" s="18" t="n"/>
-      <c r="D217" s="10" t="n"/>
-      <c r="E217" s="11" t="n"/>
-      <c r="F217" s="11" t="n"/>
-      <c r="G217" s="11" t="n"/>
-      <c r="H217" s="11" t="n"/>
-      <c r="I217" s="12" t="n"/>
-    </row>
-    <row r="218">
-      <c r="B218" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C218" s="18" t="n"/>
-      <c r="D218" s="10" t="n"/>
-      <c r="E218" s="11" t="n"/>
-      <c r="F218" s="11" t="n"/>
-      <c r="G218" s="11" t="n"/>
-      <c r="H218" s="11" t="n"/>
-      <c r="I218" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -6332,23 +6162,23 @@
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>Lists!$A$2:$A$21</formula1>
     </dataValidation>
-    <dataValidation sqref="E10:E218" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E10:E212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$B$2:$B$12</formula1>
     </dataValidation>
-    <dataValidation sqref="F10:F218" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F10:F212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$D$2:$D$31</formula1>
     </dataValidation>
-    <dataValidation sqref="H10:H218" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H10:H212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$C$2:$C$15</formula1>
     </dataValidation>
-    <dataValidation sqref="G10:G218" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="G10:G212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation sqref="C10:C218" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThanOrEqual">
+    <dataValidation sqref="C10:C212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThanOrEqual">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D10:D218" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="time" operator="between">
+    <dataValidation sqref="D10:D212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="time" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
